--- a/output/金源/国泰海通半导体设备零部件赛道资源盘点.xlsx
+++ b/output/金源/国泰海通半导体设备零部件赛道资源盘点.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -828,119 +828,203 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
+          <t>锦州神工半导体股份有限公司</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>保荐人、主承销商（国泰君安证券）</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>已上市（688233.SH）</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2020-02-21，科创板</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>集成电路刻蚀用单晶硅材料与硅零部件，含刻蚀用硅电极（即硅气体分配盘）</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>与金源同处零部件与耗材环节；其硅电极与金源的精密气体喷头为同一功能部件的不同材料路线。该项目历经四轮问询与上市委审议意见落实函，全套问询回复已公开</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>已上市公司，公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>宁波江丰电子材料股份有限公司</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>保荐人、主承销商（国泰海通证券）</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>2025年度向特定对象发行，2026-03-19深交所审核通过</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>300666.SZ</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>超高纯金属溅射靶材与半导体设备精密零部件；募集资金总额不超过192,782.90万元，投向含集成电路设备用静电吸盘产业化项目</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>静电吸盘属半导体设备工艺零部件，与金源的加热盘同处腔体内承载与控温环节；再融资项目，说明本环节企业上市后的持续资本运作路径</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>已上市公司，公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
           <t>中微半导体设备（上海）股份有限公司</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>独家保荐机构（海通证券）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>已上市（688012.SH）</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>2019-07-22，科创板首批</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>等离子体刻蚀设备与MOCVD设备</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>刻蚀设备龙头，为金源产品的下游客户类型；同时是神州半导体与新美光的股东或客户</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>已上市公司，公开信息</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>上海硅产业集团股份有限公司</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>独家保荐机构（海通证券）</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>已上市（688126.SH）</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>2020-04-20，科创板</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>半导体硅片研发制造</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>上游材料环节，与金源不在同一环节，作为半导体材料资本化案例参考</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>已上市公司，公开信息</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>△</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>武汉新芯集成电路股份有限公司</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>联席保荐机构（国泰海通证券、华源证券）</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>科创板IPO已撤回终止</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>2024-09-30受理，2026-05-19撤回</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>特色工艺晶圆制造，原拟募资48亿元</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>下游晶圆厂环节。作为撤回案例，可用于说明何种情形下建议调整申报节奏</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>交易所已公开披露，公开信息</t>
         </is>
@@ -1659,7 +1743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1787,27 +1871,27 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>中微半导体设备（上海）</t>
+          <t>神工股份</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>688012.SH／上交所科创板</t>
+          <t>688233.SH／上交所科创板</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>招股说明书、各轮问询函及回复</t>
+          <t>招股说明书注册稿、四轮问询函及回复、上市委审议意见落实函及回复</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>海通证券独家保荐；刻蚀设备龙头，金源产品的下游客户类型</t>
+          <t>国泰君安保荐；同环节硅材料与硅零部件，四轮问询案例，全套文件已取得</t>
         </is>
       </c>
     </row>
@@ -1819,49 +1903,49 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>珂玛科技</t>
+          <t>中微半导体设备（上海）</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>301611.SZ／深交所创业板</t>
+          <t>688012.SH／上交所科创板</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>招股说明书注册稿、各轮问询函及回复</t>
+          <t>招股说明书、各轮问询函及回复</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>先进陶瓷零部件与陶瓷加热器，2024年案例，用于对比两年内审核尺度变化</t>
+          <t>海通证券独家保荐；刻蚀设备龙头，金源产品的下游客户类型</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>武汉新芯集成电路</t>
+          <t>珂玛科技</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>上交所科创板／已撤回</t>
+          <t>301611.SZ／深交所创业板</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>各轮问询函及回复</t>
+          <t>招股说明书注册稿、各轮问询函及回复</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>国泰海通联席保荐的撤回案例，可用于说明申报节奏判断</t>
+          <t>先进陶瓷零部件与陶瓷加热器，2024年案例，用于对比两年内审核尺度变化</t>
         </is>
       </c>
     </row>
@@ -1873,20 +1957,47 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
+          <t>武汉新芯集成电路</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>上交所科创板／已撤回</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>各轮问询函及回复</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>国泰海通联席保荐的撤回案例，可用于说明申报节奏判断</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
           <t>上海硅产业集团</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>688126.SH／上交所科创板</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>招股说明书、问询函及回复</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>海通证券独家保荐，半导体材料资本化案例</t>
         </is>

--- a/output/金源/国泰海通半导体设备零部件赛道资源盘点.xlsx
+++ b/output/金源/国泰海通半导体设备零部件赛道资源盘点.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -912,77 +912,77 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>上海正帆科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>保荐机构、主承销商（国泰君安证券）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>已上市（688596.SH）</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2020-08-20，科创板</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>电子工艺设备与气体输送系统，含气柜、气体管路及电子特气；2025年营业收入49.16亿元</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>气体输送系统与金源的精密气体喷头同处工艺气体链条；2022年简易程序向特定对象发行亦由国泰君安保荐，为持续服务案例</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>已上市公司，公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
           <t>中微半导体设备（上海）股份有限公司</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>独家保荐机构（海通证券）</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>已上市（688012.SH）</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>2019-07-22，科创板首批</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>等离子体刻蚀设备与MOCVD设备</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>刻蚀设备龙头，为金源产品的下游客户类型；同时是神州半导体与新美光的股东或客户</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>已上市公司，公开信息</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>上海硅产业集团股份有限公司</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>独家保荐机构（海通证券）</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>已上市（688126.SH）</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>2020-04-20，科创板</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>半导体硅片研发制造</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>上游材料环节，与金源不在同一环节，作为半导体材料资本化案例参考</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>已上市公司，公开信息</t>
         </is>
@@ -996,35 +996,77 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
+          <t>上海硅产业集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>独家保荐机构（海通证券）</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>已上市（688126.SH）</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>2020-04-20，科创板</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>半导体硅片研发制造</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>上游材料环节，与金源不在同一环节，作为半导体材料资本化案例参考</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>已上市公司，公开信息</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
           <t>武汉新芯集成电路股份有限公司</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>联席保荐机构（国泰海通证券、华源证券）</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>科创板IPO已撤回终止</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>2024-09-30受理，2026-05-19撤回</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>特色工艺晶圆制造，原拟募资48亿元</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>下游晶圆厂环节。作为撤回案例，可用于说明何种情形下建议调整申报节奏</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>交易所已公开披露，公开信息</t>
         </is>
